--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>19875.7</v>
+        <v>19861.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>31.48</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>631.3754764930114</v>
+        <v>631.3254926891291</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1286674472011977</v>
+        <v>0.1286006575764549</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03176620076238882</v>
+        <v>0.03178639542275906</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>71.46697888047909</v>
+        <v>71.44026303058196</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>42.1219118459619</v>
+        <v>42.11389709099277</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>25.48985727279833</v>
+        <v>25.48740132288279</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16093.6707813519</v>
+        <v>16090.84619753453</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.1902840764676517</v>
+        <v>-0.1898473832522954</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>31.63126410076496</v>
+        <v>31.63066871896725</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19971.20444369677</v>
+        <v>19969.24751308862</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.004805085793041952</v>
+        <v>0.005424943387388748</v>
       </c>
     </row>
     <row r="15"/>
@@ -3834,7 +3834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3925,6 +3925,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>19861.5</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.7045454545449999</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.128600657576</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -547,7 +547,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>19861.5</v>
+        <v>19815.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>31.46</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.7045454545454546</v>
+        <v>0.6893939393939394</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>631.3254926891291</v>
+        <v>631.2663268556865</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1286006575764549</v>
+        <v>0.1283399343269629</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03178639542275906</v>
+        <v>0.03185727938834024</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>29.54545454545454</v>
+        <v>31.06060606060606</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>71.44026303058196</v>
+        <v>71.33597373078516</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>42.11389709099277</v>
+        <v>43.14321636165978</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>25.48740132288279</v>
+        <v>25.47781415653717</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16090.84619753453</v>
+        <v>16083.28615890903</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.1898473832522954</v>
+        <v>-0.1883461562109853</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>31.63066871896725</v>
+        <v>31.62834455742892</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19969.24751308862</v>
+        <v>19965.9088932942</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.005424943387388748</v>
+        <v>0.007593009156703578</v>
       </c>
     </row>
     <row r="15"/>
@@ -3834,7 +3834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3958,6 +3958,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>19815.45</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.689393939394</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.128339934327</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>19815.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>31.39</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.6893939393939394</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>631.2663268556865</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.1283399343269629</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>31.06060606060606</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>71.33597373078516</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>43.14321636165978</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>25.47781415653717</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>16083.28615890903</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>-0.1883461562109853</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>31.62834455742892</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>19965.9088932942</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.007593009156703578</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,19 +811,19 @@
       <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.5561795443568691</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.225415024923954</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.187224403700828</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="30" t="n">
         <v>0.1209889669935127</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -821,17 +836,17 @@
       <c r="B19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>-0.09526836869975108</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1818465540933626</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.1831239458421839</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,19 +859,19 @@
       <c r="B20" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.04134798582791488</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1585951404409121</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.2010559609298046</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.1202374612224453</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,17 +884,17 @@
       <c r="B21" t="n">
         <v>6</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>-0.136198669499495</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1846682876920349</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1826750920611252</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,21 +907,20 @@
       <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>-0.03366819678000704</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.2346113109100361</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1569201316066571</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1042,16 +1056,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>8565.1</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>64.61</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1061,16 +1075,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>9267.200000000001</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>55.65</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1080,16 +1094,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>9733.75</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>41.11</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1099,16 +1113,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>10522.1</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>32.77</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1118,16 +1132,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>10263</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>32.09</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1137,16 +1151,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>10890</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>28.01</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1156,16 +1170,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>10766.85</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>29.52</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1175,16 +1189,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>10660.9</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>29.92</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1194,16 +1208,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>11289</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>32.11</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1213,16 +1227,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>11116.45</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>31.43</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1232,16 +1246,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>9844.65</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>26.74</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1251,16 +1265,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>10436.25</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>24.71</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1270,16 +1284,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>10256.95</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>24.27</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1289,16 +1303,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>9208.5</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>20.22</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1308,16 +1322,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>8445.25</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>18.64</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1327,16 +1341,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>9171.200000000001</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>19.29</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1346,16 +1360,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>9621.950000000001</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>17.55</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1365,16 +1379,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>9441.799999999999</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>16.72</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1384,16 +1398,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>9686.1</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>16.98</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1403,16 +1417,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>9976.049999999999</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>17.12</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1422,16 +1436,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>9731.299999999999</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>16.78</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1441,16 +1455,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>9501.75</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>16.39</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1460,16 +1474,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>9155.6</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>15.89</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1479,16 +1493,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>8994.75</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>16.17</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1498,16 +1512,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>9672.549999999999</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>17.36</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1517,16 +1531,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>10166.1</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>18.67</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1536,16 +1550,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>10837.1</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>19.66</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1555,16 +1569,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>11702.85</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>21.86</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1574,16 +1588,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>12243.65</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>22.69</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1593,16 +1607,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>12748.5</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>26.14</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1612,16 +1626,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>12649.9</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>24.53</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1631,16 +1645,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>14171.35</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>26.81</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1650,16 +1664,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>15143.65</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>28.74</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1669,16 +1683,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>16026.3</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>29.51</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1688,16 +1702,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>15976.2</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>29.44</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1707,16 +1721,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>15270.45</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>25.52</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1726,16 +1740,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>17011.8</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>28.09</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1745,16 +1759,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>16696.7</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>26.33</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1764,16 +1778,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>18317.7</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>29.28</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1783,16 +1797,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>19137.65</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>30.34</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1802,16 +1816,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>19307.1</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>30.28</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1821,16 +1835,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>19179.65</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>35.76</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1840,16 +1854,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>18602.6</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>35.13</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1859,16 +1873,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>18650.95</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>34.54</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1878,16 +1892,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>18769.2</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>34.68</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1897,16 +1911,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>16910.5</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>29.64</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1916,16 +1930,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>14700.2</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>25.19</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1935,16 +1949,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>16095.7</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>28.92</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1954,16 +1968,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>16448.85</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>29.5</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1973,16 +1987,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>17883.3</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>31.65</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1992,16 +2006,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>19075.1</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>33.69</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2011,16 +2025,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>17966.85</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>31.66</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2030,16 +2044,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>17227</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>30.79</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2049,16 +2063,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>17562.75</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>30.33</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2068,16 +2082,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>18380.8</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>31.8</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2087,16 +2101,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>17829.25</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>32.07</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2106,16 +2120,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>17713.95</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>32.18</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2125,16 +2139,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>16879.1</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>30.03</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2144,16 +2158,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>16928.9</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>30.14</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2163,16 +2177,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>15203.8</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>25.91</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2182,16 +2196,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>18007.15</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>30.36</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2201,16 +2215,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>18138.8</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>30.54</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2220,16 +2234,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>18863.1</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>32.52</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2239,16 +2253,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>19339.65</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>32.19</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2258,16 +2272,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>19931.65</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>31.57</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2369,13 +2383,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>5653.3</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>25.08</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2383,12 +2397,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,C2)+1)/2)/COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2396,28 +2410,28 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16" t="n"/>
+      <c r="L2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>4884.85</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>43.18</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2425,12 +2439,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,C3)+1)/2)/COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2438,28 +2452,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>7177.75</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>71.79000000000001</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2467,12 +2481,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,C4)+1)/2)/COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2480,28 +2494,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>6150.95</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>119.84</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2509,12 +2523,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,C5)+1)/2)/COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2522,28 +2536,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>6449.15</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>34.39</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2551,15 +2565,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,C6)+1)/2)/COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2567,28 +2581,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>6672.55</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>30.47</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2596,15 +2610,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,C7)+1)/2)/COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2612,28 +2626,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>6200.15</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>36.12</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2641,15 +2655,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,C8)+1)/2)/COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2657,28 +2671,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>5593.75</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>64.2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2686,15 +2700,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,C9)+1)/2)/COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2702,28 +2716,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>5834.75</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>100.44</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2731,15 +2745,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,C10)+1)/2)/COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2747,42 +2761,42 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>3594.7</v>
       </c>
-      <c r="C11" s="7" t="n"/>
+      <c r="C11" s="25" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,C11)+1)/2)/COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2790,28 +2804,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>4614.95</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>18.19</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2819,15 +2833,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,C12)+1)/2)/COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2835,28 +2849,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>5822.95</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>72.12</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2864,15 +2878,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,C13)+1)/2)/COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2880,28 +2894,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>7087.6</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>37.92</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2909,15 +2923,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,C14)+1)/2)/COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2925,28 +2939,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>8113.15</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>55.94</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2954,15 +2968,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,C15)+1)/2)/COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2970,28 +2984,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>9733.75</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>41.11</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2999,15 +3013,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,C16)+1)/2)/COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3015,28 +3029,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>10890</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>28.01</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3044,15 +3058,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,C17)+1)/2)/COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3060,25 +3074,25 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
+      <c r="K17" s="30" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>11289</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>32.11</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3086,15 +3100,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,C18)+1)/2)/COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3102,25 +3116,25 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>10436.25</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>24.71</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3128,15 +3142,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,C19)+1)/2)/COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3144,25 +3158,25 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
+      <c r="K19" s="30" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>8445.25</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>18.64</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3170,15 +3184,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,C20)+1)/2)/COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3186,25 +3200,25 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>9441.799999999999</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>16.72</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3212,15 +3226,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,C21)+1)/2)/COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3228,25 +3242,25 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>9731.299999999999</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>16.78</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3254,15 +3268,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,C22)+1)/2)/COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3270,25 +3284,25 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>8994.75</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>16.17</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3296,15 +3310,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,C23)+1)/2)/COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3312,25 +3326,25 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>10837.1</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>19.66</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3338,15 +3352,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,C24)+1)/2)/COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3354,25 +3368,25 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>12748.5</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>26.14</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3380,15 +3394,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,C25)+1)/2)/COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3396,22 +3410,22 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="J25" s="30" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>15143.65</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>28.74</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3419,15 +3433,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,C26)+1)/2)/COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3435,22 +3449,22 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="J26" s="30" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>15270.45</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>25.52</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3458,15 +3472,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,C27)+1)/2)/COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3474,22 +3488,22 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>18317.7</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>29.28</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3497,15 +3511,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,C28)+1)/2)/COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3513,22 +3527,22 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="J28" s="30" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>19179.65</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>35.76</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3536,15 +3550,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,C29)+1)/2)/COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3552,22 +3566,22 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>18769.2</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>34.68</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3575,15 +3589,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,C30)+1)/2)/COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3591,22 +3605,22 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>16095.7</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>28.92</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3614,15 +3628,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,C31)+1)/2)/COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3630,22 +3644,22 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>19075.1</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>33.69</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3653,15 +3667,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,C32)+1)/2)/COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3669,22 +3683,22 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>17562.75</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>30.33</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3692,15 +3706,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,C33)+1)/2)/COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3708,19 +3722,19 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="I33" s="30" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>17713.95</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>32.18</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3728,15 +3742,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,C34)+1)/2)/COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3744,19 +3758,19 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="I34" s="30" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>15203.8</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>25.91</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3764,15 +3778,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,C35)+1)/2)/COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3780,19 +3794,19 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>18863.1</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>32.52</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3800,15 +3814,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,C36)+1)/2)/COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3816,10 +3830,10 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="I36" s="30" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3896,30 +3910,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>19875.7</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>31.48</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.7045454545449999</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.128667447201</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -3929,30 +3943,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>19861.5</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>31.46</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.7045454545449999</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.128600657576</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -3962,30 +3976,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>19815.45</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>31.39</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.689393939394</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.128339934327</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4105,4 +4119,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Smallcap 100 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4018,6 +4021,2112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E105"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Smallcap 100 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Aarti Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aditya Birla Real Estate Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Afcons Infrastructure Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AFCONS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Affle 3i Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AFFLE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Amber Enterprises India Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anand Rathi Wealth Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Anant Raj Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ANANTRAJ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Angel One Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Aptus Value Housing Finance India Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>APTUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ather Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bandhan Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BEML Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BLS International Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BLS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brainbees Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FIRSTCRY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brigade Enterprises Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BRIGADE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capri Global Capital Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CGCL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Castrol India Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Central Depository Services (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CESC Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CHOLAHLDNG</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>City Union Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CUB</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cohance Lifesciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>COHANCE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Computer Age Management Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CreditAccess Grameen Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CREDITACC</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Crompton Greaves Consumer Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Data Patterns (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deepak Fertilisers &amp; Petrochemicals Corp. Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEEPAKFERT</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Delhivery Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Devyani International Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEVYANI</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dr. Lal Path Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Firstsource Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FSL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Five-Star Business Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FIVESTAR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Force Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FORCEMOT</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Garden Reach Shipbuilders &amp; Engineers Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GRSE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gland Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Godawari Power &amp; Ispat Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GPIL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Great Eastern Shipping Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Gujarat Mineral Development Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GMDCLTD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HBL Engineering Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hindustan Copper Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IDBI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IDBI</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IFCI Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>IFCI</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IIFL Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Indraprastha Gas Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Inox Wind Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INOXWIND</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Inventurus Knowledge Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IRCON International Ltd.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IRCON</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ITI Ltd.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JBM Auto Ltd.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>JBMA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JM Financial Ltd.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>JMFINANCIL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>JSW Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>JSWCEMENT</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation Ltd.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>JYOTICNC</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Karur Vysya Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KARURVYSYA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kaynes Technology India Ltd.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kec International Ltd.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>KEC</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kfin Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Manappuram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MRPL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Meesho Ltd.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MEESHO</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Narayana Hrudayalaya Ltd.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NATCO Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Navin Fluorine International Ltd.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NBCC (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Netweb Technologies India Ltd.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Neuland Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>NEULANDLAB</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nuvama Wealth Management Ltd.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ola Electric Mobility Ltd.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>OLAELEC</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PG Electroplast Ltd.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Physicswallah Ltd.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pine Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Piramal Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PIRAMALFIN</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Piramal Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PNB Housing Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Poonawalla Fincorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RBL Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Redington Ltd.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Reliance Power Ltd.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>RPOWER</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sagility Ltd.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sai Life Sciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Sarda Energy and Minerals Ltd.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SARDAEN</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Signatureglobal (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SIGNATURE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sona BLW Precision Forgings Ltd.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Star Health and Allied Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>STARHEALTH</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Swan Corp Ltd.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SWANCORP</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Syngene International Ltd.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tata Chemicals Ltd.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tata Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tenneco Clean Air India Ltd.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TENNIND</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>The Ramco Cements Ltd.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>RAMCOCEM</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Triveni Turbine Ltd.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Urban Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>URBANCO</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Welspun Corp Ltd.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Whirlpool of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wockhardt Ltd.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>WOCKPHARMA</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Zensar Technolgies Ltd.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ZENSARTECH</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4119,43 +6228,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Smallcap 100 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19815.45</v>
+        <v>19991.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.39</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6893939393939394</v>
+        <v>0.75</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>631.2663268556865</v>
+        <v>631.2440795705714</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1283399343269629</v>
+        <v>0.1291207469994033</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03185727938834024</v>
+        <v>0.03157562361856647</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>31.06060606060606</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>71.33597373078516</v>
+        <v>71.64829879976133</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>43.14321636165978</v>
+        <v>38.9944896399284</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.47781415653717</v>
+        <v>25.50652575394949</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16083.28615890903</v>
+        <v>16100.84337259492</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1883461562109853</v>
+        <v>-0.1946155429760188</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.62834455742892</v>
+        <v>31.65816311808505</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19965.9088932942</v>
+        <v>19984.02803837061</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.007593009156703578</v>
+        <v>-0.000373756928163993</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4008,6 +4008,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>19991.5</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.129120746999</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19991.5</v>
+        <v>19684.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.67</v>
+        <v>31.18</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.75</v>
+        <v>0.6893939393939394</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>631.2440795705714</v>
+        <v>631.3261706221937</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1291207469994033</v>
+        <v>0.1292180399904423</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03157562361856647</v>
+        <v>0.03207184092366902</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>25</v>
+        <v>31.06060606060606</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>71.64829879976133</v>
+        <v>71.68721599617693</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>38.9944896399284</v>
+        <v>43.24858904127731</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.50652575394949</v>
+        <v>25.51010335621998</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16100.84337259492</v>
+        <v>16105.19586405873</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1946155429760188</v>
+        <v>-0.1818440232129578</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.65816311808505</v>
+        <v>31.63617224220052</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19984.02803837061</v>
+        <v>19972.74347481259</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.000373756928163993</v>
+        <v>0.01463028358564822</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4041,6 +4041,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>19684.75</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.689393939394</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.12921803999</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4081,7 +4114,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19684.75</v>
+        <v>19715.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.18</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>631.3261706221937</v>
+        <v>631.2920268972142</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1292180399904423</v>
+        <v>0.128938532415761</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03207184092366902</v>
+        <v>0.03202049311559398</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>71.68721599617693</v>
+        <v>71.57541296630441</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>43.24858904127731</v>
+        <v>43.21504813231556</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.51010335621998</v>
+        <v>25.49982546340241</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16105.19586405873</v>
+        <v>16097.8365023165</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1818440232129578</v>
+        <v>-0.1834830143002749</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.63617224220052</v>
+        <v>31.6336806318205</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19972.74347481259</v>
+        <v>19970.09036428111</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.01463028358564822</v>
+        <v>0.01292605289210691</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4074,6 +4074,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>19715.25</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.689393939394</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.128938532416</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4114,7 +4147,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19715.25</v>
+        <v>19351.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.23</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6893939393939394</v>
+        <v>0.6742424242424242</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>631.2920268972142</v>
+        <v>631.3572593800978</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.128938532415761</v>
+        <v>0.1292662401772615</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03202049311559398</v>
+        <v>0.03262642740619903</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>31.06060606060606</v>
+        <v>32.57575757575758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>71.57541296630441</v>
+        <v>71.70649607090461</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>43.21504813231556</v>
+        <v>44.31497912430169</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.49982546340241</v>
+        <v>25.51187574594673</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16097.8365023165</v>
+        <v>16107.10795260652</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1834830143002749</v>
+        <v>-0.1676386379788994</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.6336806318205</v>
+        <v>31.6366019124373</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19970.09036428111</v>
+        <v>19973.99827953558</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.01292605289210691</v>
+        <v>0.03218929567495277</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4107,6 +4107,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>19351.1</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.674242424242</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.129266240177</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4147,7 +4180,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19351.1</v>
+        <v>19193.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.65</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6742424242424242</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>631.3572593800978</v>
+        <v>631.3667763157895</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1292662401772615</v>
+        <v>0.1289922267974728</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03262642740619903</v>
+        <v>0.03289473684210526</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>32.57575757575758</v>
+        <v>34.09090909090909</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>71.70649607090461</v>
+        <v>71.59689071898912</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>44.31497912430169</v>
+        <v>45.3427035793331</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.51187574594673</v>
+        <v>25.50179988252421</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16107.10795260652</v>
+        <v>16100.98918207969</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1676386379788994</v>
+        <v>-0.1611250038643351</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.6366019124373</v>
+        <v>31.63415927888033</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19973.99827953558</v>
+        <v>19972.75716536689</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03218929567495277</v>
+        <v>0.04059734470001075</v>
       </c>
     </row>
     <row r="16">
@@ -3851,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4140,6 +4140,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>19193.55</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.659090909091</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.128992226797</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4180,7 +4213,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4270,17 +4303,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aditya Birla Real Estate Ltd.</t>
+          <t>Acutaas Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4310,17 +4343,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Afcons Infrastructure Ltd.</t>
+          <t>Affle 3i Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AFCONS</t>
+          <t>AFFLE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -4330,17 +4363,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4350,17 +4383,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4403,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Anand Rathi Wealth Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4390,17 +4423,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anand Rathi Wealth Ltd.</t>
+          <t>Anant Raj Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -4410,17 +4443,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anant Raj Ltd.</t>
+          <t>Angel One Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4430,17 +4463,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Angel One Ltd.</t>
+          <t>Apollo Tyres Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4450,17 +4483,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aptus Value Housing Finance India Ltd.</t>
+          <t>Ather Energy Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4470,17 +4503,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aster DM Quality Care Ltd.</t>
+          <t>Avanti Feeds Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4490,17 +4523,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ather Energy Ltd.</t>
+          <t>Bandhan Bank Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4510,17 +4543,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bandhan Bank Ltd.</t>
+          <t>Belrise Industries Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4550,17 +4583,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BLS International Services Ltd.</t>
+          <t>Bharat Coking Coal Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BLS</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4570,17 +4603,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Brainbees Solutions Ltd.</t>
+          <t>Brigade Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FIRSTCRY</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -4590,17 +4623,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Brigade Enterprises Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4610,17 +4643,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>Cemindia Projects Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -4630,17 +4663,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Central Depository Services (India) Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4650,17 +4683,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Ltd.</t>
+          <t>Central Mine Planning &amp; Design Institute Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>CMPDI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4690,17 +4723,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>Chennai Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4830,17 +4863,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Data Patterns (India) Ltd.</t>
+          <t>Cupid Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DATAPATTNS</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4850,17 +4883,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deepak Fertilisers &amp; Petrochemicals Corp. Ltd.</t>
+          <t>Data Patterns (India) Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DEEPAKFERT</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4870,17 +4903,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Delhivery Ltd.</t>
+          <t>Deepak Fertilisers &amp; Petrochemicals Corp. Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>DEEPAKFERT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -4890,17 +4923,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Devyani International Ltd.</t>
+          <t>Delhivery Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DEVYANI</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4910,17 +4943,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>Devyani International Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -4930,17 +4963,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Firstsource Solutions Ltd.</t>
+          <t>Dr. Lal Path Labs Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4950,17 +4983,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>Emmvee Photovoltaic Power Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>EMMVEE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4970,17 +5003,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Force Motors Ltd.</t>
+          <t>Firstsource Solutions Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4990,17 +5023,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Garden Reach Shipbuilders &amp; Engineers Ltd.</t>
+          <t>Force Motors Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5010,17 +5043,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gland Pharma Ltd.</t>
+          <t>Gallantt Ispat Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5063,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Godawari Power &amp; Ispat Ltd.</t>
+          <t>Garden Reach Shipbuilders &amp; Engineers Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>GRSE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5050,17 +5083,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Great Eastern Shipping Co. Ltd.</t>
+          <t>Gland Pharma Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5070,17 +5103,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gujarat Mineral Development Corporation Ltd.</t>
+          <t>Godawari Power &amp; Ispat Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>GPIL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5090,17 +5123,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HBL Engineering Ltd.</t>
+          <t>Great Eastern Shipping Co. Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5110,17 +5143,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Ltd.</t>
+          <t>Gujarat Mineral Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HSCL</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5130,17 +5163,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hindustan Copper Ltd.</t>
+          <t>HBL Engineering Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HBLENGINE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5150,17 +5183,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd.</t>
+          <t>HFCL Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5170,17 +5203,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IFCI Ltd.</t>
+          <t>Himadri Speciality Chemical Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>HSCL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5190,12 +5223,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IIFL Finance Ltd.</t>
+          <t>IDBI Bank Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>IDBI</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5210,17 +5243,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>IFCI Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5230,17 +5263,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Inox Wind Ltd.</t>
+          <t>IIFL Finance Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5250,17 +5283,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inventurus Knowledge Solutions Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IKS</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5270,17 +5303,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IRCON International Ltd.</t>
+          <t>Inox Wind Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IRCON</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5290,17 +5323,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ITI Ltd.</t>
+          <t>Inventurus Knowledge Solutions Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5310,17 +5343,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JBM Auto Ltd.</t>
+          <t>ITI Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>ITI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5330,17 +5363,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JM Financial Ltd.</t>
+          <t>JBM Auto Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5470,17 +5503,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Manappuram Finance Ltd.</t>
+          <t>Kirloskar Oil Eng Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5490,17 +5523,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
+          <t>KPIT Technologies Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5510,17 +5543,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Meesho Ltd.</t>
+          <t>Manappuram Finance Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5530,17 +5563,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Ltd.</t>
+          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5550,17 +5583,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NATCO Pharma Ltd.</t>
+          <t>MTAR Technologies Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5570,17 +5603,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5590,17 +5623,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NBCC (India) Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5610,17 +5643,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Netweb Technologies India Ltd.</t>
+          <t>NBCC (India) Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -5630,17 +5663,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Neuland Laboratories Ltd.</t>
+          <t>Netweb Technologies India Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5650,17 +5683,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nuvama Wealth Management Ltd.</t>
+          <t>Neuland Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5703,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Ltd.</t>
+          <t>Nuvama Wealth Management Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5690,17 +5723,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PG Electroplast Ltd.</t>
+          <t>Ola Electric Mobility Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5710,17 +5743,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Physicswallah Ltd.</t>
+          <t>Onesource Specialty Pharma Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PWL</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5730,17 +5763,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pine Labs Ltd.</t>
+          <t>PG Electroplast Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5750,17 +5783,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Piramal Finance Ltd.</t>
+          <t>Physicswallah Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5770,17 +5803,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Piramal Pharma Ltd.</t>
+          <t>Pine Labs Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5790,17 +5823,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PNB Housing Finance Ltd.</t>
+          <t>Piramal Pharma Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5810,12 +5843,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>PNB Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5830,12 +5863,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5850,17 +5883,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Redington Ltd.</t>
+          <t>R R Kabel Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5870,17 +5903,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Reliance Power Ltd.</t>
+          <t>RBL Bank Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RPOWER</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5890,17 +5923,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sagility Ltd.</t>
+          <t>Redington Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SAGILITY</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5910,17 +5943,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sai Life Sciences Ltd.</t>
+          <t>Sagility Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5930,17 +5963,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sarda Energy and Minerals Ltd.</t>
+          <t>Sai Life Sciences Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5950,17 +5983,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Signatureglobal (India) Ltd.</t>
+          <t>Sammaan Capital Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SIGNATURE</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5990,17 +6023,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Star Health and Allied Insurance Company Ltd.</t>
+          <t>Sterlite Technologies Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -6010,17 +6043,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Swan Corp Ltd.</t>
+          <t>Syngene International Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SWANCORP</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6063,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Syngene International Ltd.</t>
+          <t>Syrma SGS Technology Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6070,12 +6103,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Technologies Ltd.</t>
+          <t>Tata Elxsi Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TATATECH</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6090,17 +6123,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tenneco Clean Air India Ltd.</t>
+          <t>Tata Technologies Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TENNIND</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6143,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>TD Power Systems Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6130,17 +6163,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Triveni Turbine Ltd.</t>
+          <t>Tenneco Clean Air India Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TRITURBINE</t>
+          <t>TENNIND</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6150,17 +6183,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Urban Company Ltd.</t>
+          <t>Triveni Turbine Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>URBANCO</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6170,17 +6203,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Welspun Corp Ltd.</t>
+          <t>Urban Company Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>URBANCO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6190,17 +6223,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Whirlpool of India Ltd.</t>
+          <t>Vedanta Power Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WHIRLPOOL</t>
+          <t>VEDPOWER</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6210,17 +6243,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Wockhardt Ltd.</t>
+          <t>Welspun Corp Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WOCKPHARMA</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6230,17 +6263,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Zensar Technolgies Ltd.</t>
+          <t>Wockhardt Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>WOCKPHARMA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19193.55</v>
+        <v>19245.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.4</v>
+        <v>37.71</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6590909090909091</v>
+        <v>0.9402985074626866</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>631.3667763157895</v>
+        <v>510.3606470432246</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1289922267974728</v>
+        <v>-0.1186324223244649</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03289473684210526</v>
+        <v>0.02651816494298594</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>34.09090909090909</v>
+        <v>5.970149253731338</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>71.59689071898912</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45.3427035793331</v>
+        <v>10.17910447761194</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.50179988252421</v>
+        <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16100.98918207969</v>
+        <v>8712.876966321932</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1611250038643351</v>
+        <v>-0.5472818880933439</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.63415927888033</v>
+        <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19972.75716536689</v>
+        <v>15065.55466606054</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.04059734470001075</v>
+        <v>-0.2171989241201652</v>
       </c>
     </row>
     <row r="16">
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>-0.09526836869975108</v>
+        <v>-0.02061304220933613</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1818465540933626</v>
+        <v>0.1607825722862346</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.1831239458421839</v>
@@ -860,16 +860,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.04134798582791488</v>
+        <v>-0.007032164631225468</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>0.1585951404409121</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.2010559609298046</v>
+        <v>0.1608415893610784</v>
       </c>
       <c r="F20" s="30" t="n">
         <v>0.1202374612224453</v>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>-0.136198669499495</v>
+        <v>-0.0111139653265252</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>0.1846682876920349</v>
@@ -911,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>-0.03366819678000704</v>
+        <v>-0.05622242823348889</v>
       </c>
       <c r="D22" s="30" t="n">
         <v>0.2346113109100361</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
@@ -971,7 +971,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2290,6 +2290,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>19245.7</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2306,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2406,7 +2425,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,C2)+1)/2)/COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,C2)+1)/2)/COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2448,7 +2467,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,C3)+1)/2)/COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,C3)+1)/2)/COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2490,7 +2509,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,C4)+1)/2)/COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,C4)+1)/2)/COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2532,7 +2551,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,C5)+1)/2)/COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,C5)+1)/2)/COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2577,7 +2596,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,C6)+1)/2)/COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,C6)+1)/2)/COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2622,7 +2641,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,C7)+1)/2)/COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,C7)+1)/2)/COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2667,7 +2686,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,C8)+1)/2)/COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,C8)+1)/2)/COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2712,7 +2731,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,C9)+1)/2)/COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,C9)+1)/2)/COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2757,7 +2776,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,C10)+1)/2)/COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,C10)+1)/2)/COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2800,7 +2819,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,C11)+1)/2)/COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,C11)+1)/2)/COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2845,7 +2864,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,C12)+1)/2)/COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,C12)+1)/2)/COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2890,7 +2909,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,C13)+1)/2)/COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,C13)+1)/2)/COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2935,7 +2954,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,C14)+1)/2)/COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,C14)+1)/2)/COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2980,7 +2999,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,C15)+1)/2)/COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,C15)+1)/2)/COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3025,7 +3044,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,C16)+1)/2)/COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,C16)+1)/2)/COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3070,7 +3089,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,C17)+1)/2)/COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,C17)+1)/2)/COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3085,7 +3104,10 @@
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="30" t="n"/>
+      <c r="K17" s="30">
+        <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
@@ -3112,7 +3134,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,C18)+1)/2)/COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,C18)+1)/2)/COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3154,7 +3176,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,C19)+1)/2)/COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,C19)+1)/2)/COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3196,7 +3218,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,C20)+1)/2)/COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,C20)+1)/2)/COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3238,7 +3260,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,C21)+1)/2)/COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,C21)+1)/2)/COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3280,7 +3302,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,C22)+1)/2)/COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,C22)+1)/2)/COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3322,7 +3344,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,C23)+1)/2)/COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,C23)+1)/2)/COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3364,7 +3386,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,C24)+1)/2)/COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,C24)+1)/2)/COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3406,7 +3428,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,C25)+1)/2)/COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,C25)+1)/2)/COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3417,7 +3439,10 @@
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="30" t="n"/>
+      <c r="J25" s="30">
+        <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K25" s="30" t="n"/>
       <c r="L25" s="30" t="n"/>
     </row>
@@ -3445,7 +3470,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,C26)+1)/2)/COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,C26)+1)/2)/COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3484,7 +3509,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,C27)+1)/2)/COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,C27)+1)/2)/COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3523,7 +3548,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,C28)+1)/2)/COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,C28)+1)/2)/COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3562,7 +3587,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,C29)+1)/2)/COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,C29)+1)/2)/COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3601,7 +3626,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,C30)+1)/2)/COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,C30)+1)/2)/COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3640,7 +3665,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,C31)+1)/2)/COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,C31)+1)/2)/COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3679,7 +3704,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,C32)+1)/2)/COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,C32)+1)/2)/COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3718,14 +3743,17 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,C33)+1)/2)/COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,C33)+1)/2)/COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="30" t="n"/>
+      <c r="I33" s="30">
+        <f>IFERROR(B37/B33-1,"")</f>
+        <v/>
+      </c>
       <c r="J33" s="30" t="n"/>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
@@ -3754,7 +3782,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,C34)+1)/2)/COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,C34)+1)/2)/COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3790,7 +3818,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,C35)+1)/2)/COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,C35)+1)/2)/COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3826,7 +3854,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,C36)+1)/2)/COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,C36)+1)/2)/COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3837,6 +3865,42 @@
       <c r="J36" s="30" t="n"/>
       <c r="K36" s="30" t="n"/>
       <c r="L36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <v>19245.7</v>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E37" s="33">
+        <f>IFERROR(B37/C37,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="30">
+        <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,C37)+1)/2)/COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I37" s="30" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3851,15 +3915,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4173,6 +4237,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>19245.7</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.940298507463</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>-0.118632422324</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4213,7 +4310,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19245.7</v>
+        <v>19058.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.71</v>
+        <v>37.37</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9402985074626866</v>
+        <v>0.9328358208955224</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>510.3606470432246</v>
+        <v>509.9986620283651</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1186324223244649</v>
+        <v>-0.1193573398181628</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02651816494298594</v>
+        <v>0.02675943270002676</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>5.970149253731338</v>
+        <v>6.716417910447758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>10.17910447761194</v>
+        <v>10.70149253731343</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8712.876966321932</v>
+        <v>8706.69715814825</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5472818880933439</v>
+        <v>-0.543162964945143</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15065.55466606054</v>
+        <v>15054.86907527046</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2171989241201652</v>
+        <v>-0.21007683779961</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4270,6 +4270,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>19058.65</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>-0.119357339818</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4310,7 +4343,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19058.65</v>
+        <v>19149.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.37</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>509.9986620283651</v>
+        <v>510.0985615343633</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1193573398181628</v>
+        <v>-0.1192185659832927</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02675943270002676</v>
+        <v>0.02663825253063399</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8706.69715814825</v>
+        <v>8708.402642514653</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.543162964945143</v>
+        <v>-0.5452317527970163</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15054.86907527046</v>
+        <v>15057.8180516021</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.21007683779961</v>
+        <v>-0.2136540071542734</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4303,6 +4303,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>19149.1</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>-0.119218565983</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4343,7 +4376,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19149.1</v>
+        <v>19448.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.54</v>
+        <v>38.13</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9328358208955224</v>
+        <v>0.9477611940298507</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>510.0985615343633</v>
+        <v>510.0629425649095</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1192185659832927</v>
+        <v>-0.1191708690119896</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02663825253063399</v>
+        <v>0.02622606871230002</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>6.716417910447758</v>
+        <v>5.223880597014929</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>10.70149253731343</v>
+        <v>9.656716417910451</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8708.402642514653</v>
+        <v>8707.794555468137</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5452317527970163</v>
+        <v>-0.5522685549436139</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15057.8180516021</v>
+        <v>15056.76659997752</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2136540071542734</v>
+        <v>-0.2258214379378817</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4336,6 +4336,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>19448.7</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>-0.119170869012</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4376,7 +4409,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19448.7</v>
+        <v>19506.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>38.13</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>510.0629425649095</v>
+        <v>509.9856209150327</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1191708690119896</v>
+        <v>-0.1191791660297321</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02622606871230002</v>
+        <v>0.0261437908496732</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8707.794555468137</v>
+        <v>8706.474520261439</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5522685549436139</v>
+        <v>-0.553673202614379</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15056.76659997752</v>
+        <v>15054.48410905696</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2258214379378817</v>
+        <v>-0.2282502334267039</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4369,6 +4369,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>19506.95</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>-0.11917916603</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4409,7 +4442,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19506.95</v>
+        <v>19050.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>38.25</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9477611940298507</v>
+        <v>0.9328358208955224</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>509.9856209150327</v>
+        <v>510.0428380187416</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1191791660297321</v>
+        <v>-0.1190723790829198</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0261437908496732</v>
+        <v>0.02677376171352075</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>5.223880597014929</v>
+        <v>6.716417910447758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>9.656716417910451</v>
+        <v>10.70149253731343</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8706.474520261439</v>
+        <v>8707.451330655958</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.553673202614379</v>
+        <v>-0.5429183400267736</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15054.48410905696</v>
+        <v>15056.17312526296</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2282502334267039</v>
+        <v>-0.2096538535092751</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4402,6 +4402,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>19050.1</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>-0.119072379083</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4442,7 +4475,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19050.1</v>
+        <v>19153.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.35</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>510.0428380187416</v>
+        <v>510.0852197070573</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1190723790829198</v>
+        <v>-0.1192650864018366</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02677376171352075</v>
+        <v>0.02663115845539281</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8707.451330655958</v>
+        <v>8708.174870838884</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5429183400267736</v>
+        <v>-0.5453528628495339</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15056.17312526296</v>
+        <v>15057.42420848393</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2096538535092751</v>
+        <v>-0.2138634202016357</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4435,6 +4435,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>19153.7</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.119265086402</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4475,7 +4508,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19153.7</v>
+        <v>19425.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.55</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9328358208955224</v>
+        <v>0.9477611940298507</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>510.0852197070573</v>
+        <v>509.9973746390128</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1192650864018366</v>
+        <v>-0.1194115924554763</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02663115845539281</v>
+        <v>0.02625360987135731</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>6.716417910447758</v>
+        <v>5.223880597014929</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>10.70149253731343</v>
+        <v>9.656716417910451</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8708.174870838884</v>
+        <v>8706.675179837228</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5453528628495339</v>
+        <v>-0.5517983722761879</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15057.42420848393</v>
+        <v>15054.83107227244</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2138634202016357</v>
+        <v>-0.2250084386603158</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4468,6 +4468,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>19425.8</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.119411592455</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4508,7 +4541,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19425.8</v>
+        <v>19447.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>38.09</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>509.9973746390128</v>
+        <v>513.6661384046488</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1194115924554763</v>
+        <v>-0.1129474505763629</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02625360987135731</v>
+        <v>0.02641310089804543</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8706.675179837228</v>
+        <v>8769.308314844166</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5517983722761879</v>
+        <v>-0.5490755414685683</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15054.83107227244</v>
+        <v>15163.13088219757</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2250084386603158</v>
+        <v>-0.220300354690212</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4501,6 +4501,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>19447.4</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.112947450576</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4541,7 +4574,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19447.4</v>
+        <v>19384.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.86</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>513.6661384046488</v>
+        <v>513.9130434782609</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1129474505763629</v>
+        <v>-0.1128342317917221</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02641310089804543</v>
+        <v>0.02651113467656416</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8769.308314844166</v>
+        <v>8773.523478260871</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5490755414685683</v>
+        <v>-0.5474019088016966</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15163.13088219757</v>
+        <v>15170.41937888199</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.220300354690212</v>
+        <v>-0.2174064535676412</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4534,6 +4534,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>19384.8</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>-0.112834231792</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4574,7 +4607,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19384.8</v>
+        <v>19131.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.72</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9477611940298507</v>
+        <v>0.9328358208955224</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>513.9130434782609</v>
+        <v>516.3751686909583</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1128342317917221</v>
+        <v>-0.1084502465319022</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02651113467656416</v>
+        <v>0.02699055330634278</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>5.223880597014929</v>
+        <v>6.716417910447758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>9.656716417910451</v>
+        <v>10.70149253731343</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8773.523478260871</v>
+        <v>8815.556879892041</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5474019088016966</v>
+        <v>-0.5392172739541159</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15170.41937888199</v>
+        <v>15243.09990823212</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2174064535676412</v>
+        <v>-0.2032542895700788</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4567,6 +4567,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>19131.7</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>-0.108450246532</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4607,7 +4640,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19131.7</v>
+        <v>19129.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>37.05</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>516.3751686909583</v>
+        <v>524.2477391066045</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.1084502465319022</v>
+        <v>-0.0950204069614119</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02699055330634278</v>
+        <v>0.02740476842970677</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8815.556879892041</v>
+        <v>8949.957402027954</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5392172739541159</v>
+        <v>-0.532145793368046</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15243.09990823212</v>
+        <v>15475.49368829033</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2032542895700788</v>
+        <v>-0.1910268958227304</v>
       </c>
     </row>
     <row r="16">
@@ -3915,14 +3915,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
@@ -4600,6 +4600,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>19129.8</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>-0.0950204069614</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4640,7 +4673,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19129.8</v>
+        <v>18935.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.49</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>524.2477391066045</v>
+        <v>523.3761746821448</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.0950204069614119</v>
+        <v>-0.09951942752674736</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02740476842970677</v>
+        <v>0.02763957987838585</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8949.957402027954</v>
+        <v>8935.078054173577</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.532145793368046</v>
+        <v>-0.5281370923161968</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15475.49368829033</v>
+        <v>15449.7656045171</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1910268958227304</v>
+        <v>-0.1840953960356946</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4633,6 +4633,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>18935.75</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>-0.0995194275267</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4673,7 +4706,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18935.75</v>
+        <v>18487.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>36.18</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9328358208955224</v>
+        <v>0.917910447761194</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>523.3761746821448</v>
+        <v>523.2748372487971</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.09951942752674736</v>
+        <v>-0.09416622666179131</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02763957987838585</v>
+        <v>0.02830455703368243</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>6.716417910447758</v>
+        <v>8.208955223880599</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>10.70149253731343</v>
+        <v>11.74626865671642</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8935.078054173577</v>
+        <v>8933.348021511465</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5281370923161968</v>
+        <v>-0.5167846023209736</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15449.7656045171</v>
+        <v>15446.77418139178</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1840953960356946</v>
+        <v>-0.1644656503982854</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4666,6 +4666,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>18487.3</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.9179104477609999</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>-0.0941662266618</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4706,7 +4739,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18487.3</v>
+        <v>18275.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.33</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.917910447761194</v>
+        <v>0.8880597014925373</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>523.2748372487971</v>
+        <v>527.4430014430015</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.09416622666179131</v>
+        <v>-0.08695077575308596</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02830455703368243</v>
+        <v>0.02886002886002886</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>8.208955223880599</v>
+        <v>11.19402985074627</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>11.74626865671642</v>
+        <v>13.83582089552239</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8933.348021511465</v>
+        <v>9004.506920634924</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5167846023209736</v>
+        <v>-0.5073015873015871</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15446.77418139178</v>
+        <v>15569.81600659658</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1644656503982854</v>
+        <v>-0.1480684394970108</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4699,6 +4699,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>18275.9</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.888059701493</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>-0.08695077575309999</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4739,7 +4772,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18275.9</v>
+        <v>17739.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.65</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.8880597014925373</v>
+        <v>0.8582089552238806</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>527.4430014430015</v>
+        <v>527.3320451843044</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.08695077575308596</v>
+        <v>-0.08697200763269608</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02886002886002886</v>
+        <v>0.02972651605231867</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>11.19402985074627</v>
+        <v>14.17910447761194</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>13.83582089552239</v>
+        <v>15.92537313432836</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>9004.506920634924</v>
+        <v>9002.612675386446</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5073015873015871</v>
+        <v>-0.4925089179548157</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15569.81600659658</v>
+        <v>15566.54064124342</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1480684394970108</v>
+        <v>-0.1224902327161541</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4732,6 +4732,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>17739.45</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.858208955224</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>-0.08697200763269999</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4772,7 +4805,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17739.45</v>
+        <v>17985</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>33.64</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>527.3320451843044</v>
+        <v>537.1863799283154</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.08697200763269608</v>
+        <v>-0.0700288108355579</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02972651605231867</v>
+        <v>0.02986857825567503</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>9002.612675386446</v>
+        <v>9170.845878136202</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4925089179548157</v>
+        <v>-0.4900836320191158</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15566.54064124342</v>
+        <v>15857.4349718382</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1224902327161541</v>
+        <v>-0.1182966376514762</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4765,6 +4765,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>17985</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.858208955224</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>-0.0700288108356</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4805,7 +4838,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17985</v>
+        <v>18468.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>33.48</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.8582089552238806</v>
+        <v>0.8731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>537.1863799283154</v>
+        <v>542.3994126284875</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.0700288108355579</v>
+        <v>-0.06127401206770999</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02986857825567503</v>
+        <v>0.02936857562408223</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>14.17910447761194</v>
+        <v>12.68656716417911</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>15.92537313432836</v>
+        <v>14.88059701492537</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>9170.845878136202</v>
+        <v>9259.84277239354</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4900836320191158</v>
+        <v>-0.4986196769456681</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>15857.4349718382</v>
+        <v>16011.32071827145</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1182966376514762</v>
+        <v>-0.1330564296203063</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4798,6 +4798,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>18468.7</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.873134328358</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>-0.0612740120677</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4838,7 +4871,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18468.7</v>
+        <v>18634.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.05</v>
+        <v>34.13</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>542.3994126284875</v>
+        <v>545.9976560210958</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.06127401206770999</v>
+        <v>-0.05528013731980785</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02936857562408223</v>
+        <v>0.02929973630237328</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>9259.84277239354</v>
+        <v>9321.271983592151</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4986196769456681</v>
+        <v>-0.4997949018458833</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>16011.32071827145</v>
+        <v>16117.53880708217</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1330564296203063</v>
+        <v>-0.1350885270603993</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4831,6 +4831,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>18634.9</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.873134328358</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>-0.0552801373198</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4871,7 +4904,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18634.9</v>
+        <v>18811.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.13</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>545.9976560210958</v>
+        <v>545.7310704960835</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.05528013731980785</v>
+        <v>-0.05421629698394248</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02929973630237328</v>
+        <v>0.02901073397156948</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>9321.271983592151</v>
+        <v>9316.720835509139</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4997949018458833</v>
+        <v>-0.5047287496373658</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>16117.53880708217</v>
+        <v>16109.66935471839</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1350885270603993</v>
+        <v>-0.1436197107215383</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4864,6 +4864,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>18811.35</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.873134328358</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>-0.0542162969839</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4904,7 +4937,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-100.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-100.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18811.35</v>
+        <v>18463.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.47</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.8731343283582089</v>
+        <v>0.8582089552238806</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>545.7310704960835</v>
+        <v>548.2066508313538</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.05421629698394248</v>
+        <v>-0.05227272987405707</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02901073397156948</v>
+        <v>0.02969121140142518</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>12.68656716417911</v>
+        <v>14.17910447761194</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>14.88059701492537</v>
+        <v>15.92537313432836</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>17.072</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>9316.720835509139</v>
+        <v>9358.983942992874</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.5047287496373658</v>
+        <v>-0.4931116389548693</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.51942857142857</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>16109.66935471839</v>
+        <v>16182.74707159823</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1436197107215383</v>
+        <v>-0.1235324058364439</v>
       </c>
     </row>
     <row r="16">
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4897,6 +4897,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>18463.6</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.858208955224</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>-0.0522727298741</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4937,7 +4970,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
